--- a/data/catalogue-sample.xlsx
+++ b/data/catalogue-sample.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y15"/>
+  <dimension ref="A1:Y13"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -487,16 +487,16 @@
         <v>1</v>
       </c>
       <c r="D2" t="str">
-        <v>chemises</v>
+        <v>t-shirts</v>
       </c>
       <c r="E2" t="str">
-        <v>Exemple chemise</v>
+        <v>Exemple</v>
       </c>
       <c r="H2">
-        <v>399</v>
+        <v>199</v>
       </c>
       <c r="K2" t="str">
-        <v>Blanc:#ffffff</v>
+        <v>Noir:#111111</v>
       </c>
       <c r="L2" t="str">
         <v>S;M;L</v>
@@ -528,13 +528,13 @@
         <v>pantalons</v>
       </c>
       <c r="E3" t="str">
-        <v>Exemple pantalon</v>
+        <v>Exemple 2</v>
       </c>
       <c r="H3">
-        <v>499</v>
+        <v>299</v>
       </c>
       <c r="K3" t="str">
-        <v>Beige:#cdbfa4</v>
+        <v>Noir:#111111</v>
       </c>
       <c r="L3" t="str">
         <v>S;M;L</v>
@@ -554,7 +554,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>EH-0001</v>
+        <v>EH-SNK-01</v>
       </c>
       <c r="B4" t="str">
         <v>oui</v>
@@ -566,72 +566,69 @@
         <v>nouveautes</v>
       </c>
       <c r="E4" t="str">
-        <v>Chemise Oxford Atlas</v>
+        <v>Sneaker basse toile</v>
       </c>
       <c r="F4" t="str">
-        <v>قميص أكسفورد أطلس</v>
+        <v>سنيكر واطي بالتوال</v>
       </c>
       <c r="G4" t="str">
-        <v>Atlas Oxford Shirt</v>
+        <v>Low canvas sneaker</v>
       </c>
       <c r="H4">
-        <v>450</v>
-      </c>
-      <c r="I4" t="str">
-        <v/>
+        <v>390</v>
       </c>
       <c r="J4" t="str">
         <v>Nouveauté</v>
       </c>
       <c r="K4" t="str">
-        <v>Écru:#E7E0D2|Indigo:#2E4260|Olive:#4B5540</v>
+        <v>Blanc:#FFFFFF|Noir:#111111</v>
       </c>
       <c r="L4" t="str">
-        <v>XS;S;M;L;XL;XXL</v>
+        <v>39;40;41;42;43;44;45</v>
       </c>
       <c r="M4" t="str">
-        <v>XXL</v>
+        <v>39</v>
       </c>
       <c r="N4" t="str">
-        <v>Une oxford coupée près du corps sans serrer, dans un coton lavé qui tombe déjà comme une chemise portée cent fois.</v>
+        <v>Sneaker basse en toile, semelle gomme. Toutes les pointures du 40 au 45 en stock.</v>
       </c>
       <c r="O4" t="str">
-        <v>قميص أكسفورد مقصوص قريب من الجسم بلا ما يضيق، بقطن مغسول كيطيح بحال قميص لبستيه مية مرة.</v>
+        <v>سنيكر واطي بالتوال، وسمال ديال الڭوم. كل القياسات من 40 حتى 45 موجودة.</v>
       </c>
       <c r="P4" t="str">
-        <v>An oxford cut close without pulling, in a washed cotton that already falls like a shirt worn a hundred times.</v>
+        <v>Low canvas sneaker on a gum sole. Sizes 40 to 45 in stock.</v>
       </c>
       <c r="Q4" t="str">
-        <v>100% coton oxford 140 g/m².</v>
+        <v>Toile de coton, semelle gomme.</v>
       </c>
       <c r="R4" t="str">
-        <v>100% قطن أكسفورد 140 غ/م².</v>
+        <v>توال ديال القطن، وسمال ڭوم.</v>
       </c>
       <c r="S4" t="str">
-        <v>100% oxford cotton, 140 gsm.</v>
+        <v>Cotton canvas, gum sole.</v>
       </c>
       <c r="T4" t="str">
-        <v>Lavage machine à 30°C, séchage à plat.</v>
+        <v>Brosse douce et savon.</v>
       </c>
       <c r="U4" t="str">
-        <v>غسيل فالماكينة على 30°، والتنشيف مبسوط.</v>
+        <v>فرشاة رقيقة والصابون.</v>
       </c>
       <c r="V4" t="str">
-        <v>Machine wash at 30°C, dry flat.</v>
+        <v>Soft brush and soap.</v>
       </c>
       <c r="W4" t="str">
-        <v>https://picsum.photos/seed/eh-oxford-1/1200/1600;https://picsum.photos/seed/eh-oxford-2/1200/1600</v>
+        <v/>
       </c>
       <c r="X4">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Y4">
-        <v>128</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>EH-0002</v>
+        <v>EH-HOD-01</v>
       </c>
       <c r="B5" t="str">
         <v>oui</v>
@@ -643,49 +640,49 @@
         <v>nouveautes</v>
       </c>
       <c r="E5" t="str">
-        <v>Chino Medina</v>
+        <v>Hoodie molleton épais</v>
       </c>
       <c r="F5" t="str">
-        <v>سروال شينو مدينة</v>
+        <v>هودي مبطن غليظ</v>
       </c>
       <c r="G5" t="str">
-        <v>Medina Chino</v>
+        <v>Heavy fleece hoodie</v>
       </c>
       <c r="H5">
-        <v>590</v>
+        <v>320</v>
       </c>
       <c r="I5">
-        <v>690</v>
+        <v>420</v>
       </c>
       <c r="J5" t="str">
         <v>Promo</v>
       </c>
       <c r="K5" t="str">
-        <v>Sable:#CDBFA4|Olive:#4B5540|Marine:#252F45</v>
+        <v>Gris:#767676|Noir:#111111|Blanc:#FFFFFF</v>
       </c>
       <c r="L5" t="str">
-        <v>XS;S;M;L;XL;XXL</v>
+        <v>S;M;L;XL;XXL</v>
       </c>
       <c r="M5" t="str">
-        <v>XS</v>
+        <v>XXL</v>
       </c>
       <c r="N5" t="str">
-        <v>Le chino de tous les jours : jambe droite, taille mi-haute, poches italiennes.</v>
+        <v>Molleton gratté à l'intérieur, capuche doublée, poche kangourou.</v>
       </c>
       <c r="O5" t="str">
-        <v>شينو ديال كل نهار: ساق مستقيمة، وسط متوسط، وجيوب إيطالية.</v>
+        <v>مبطن من الداخل، كابوش مدوبل، وجيب كنغورو.</v>
       </c>
       <c r="P5" t="str">
-        <v>The everyday chino: straight leg, mid rise, slant pockets.</v>
+        <v>Brushed fleece inside, lined hood, kangaroo pocket.</v>
       </c>
       <c r="Q5" t="str">
-        <v>97% coton, 3% élasthanne.</v>
+        <v>80% coton, 20% polyester.</v>
       </c>
       <c r="R5" t="str">
-        <v>97% قطن، 3% إيلاستان.</v>
+        <v>80% قطن، 20% بوليستر.</v>
       </c>
       <c r="S5" t="str">
-        <v>97% cotton, 3% elastane.</v>
+        <v>80% cotton, 20% polyester.</v>
       </c>
       <c r="T5" t="str">
         <v>Lavage à 30°C sur l'envers.</v>
@@ -697,18 +694,18 @@
         <v>Wash at 30°C inside out.</v>
       </c>
       <c r="W5" t="str">
-        <v>https://picsum.photos/seed/eh-chino-1/1200/1600;https://picsum.photos/seed/eh-chino-2/1200/1600</v>
+        <v/>
       </c>
       <c r="X5">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="Y5">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>EH-0003</v>
+        <v>EH-TEE-01</v>
       </c>
       <c r="B6" t="str">
         <v>oui</v>
@@ -720,69 +717,66 @@
         <v>nouveautes</v>
       </c>
       <c r="E6" t="str">
-        <v>Veste Tanger</v>
+        <v>T-shirt coton épais</v>
       </c>
       <c r="F6" t="str">
-        <v>جاكيط طنجة</v>
+        <v>تيشيرت قطن غليظ</v>
       </c>
       <c r="G6" t="str">
-        <v>Tangier Jacket</v>
+        <v>Heavy cotton tee</v>
       </c>
       <c r="H6">
-        <v>2450</v>
+        <v>120</v>
       </c>
       <c r="J6" t="str">
-        <v>Dernières pièces</v>
+        <v>Top vente</v>
       </c>
       <c r="K6" t="str">
-        <v>Havane:#6B4A32|Olive:#4B5540</v>
+        <v>Blanc:#FFFFFF|Noir:#111111|Gris:#767676</v>
       </c>
       <c r="L6" t="str">
         <v>S;M;L;XL</v>
       </c>
-      <c r="M6" t="str">
-        <v/>
-      </c>
       <c r="N6" t="str">
-        <v>Blouson court en velours de cuir, épaules nettes et taille resserrée par une patte boutonnée.</v>
+        <v>Coton 240 g, coupe droite, col côtelé qui ne se détend pas.</v>
       </c>
       <c r="O6" t="str">
-        <v>جاكيط قصير من جلد الشامواه، أكتاف واضحة ووسط مشدود بحزام مزرر.</v>
+        <v>قطن 240 غ، قصة مستقيمة، وياقة ما كتتمططش.</v>
       </c>
       <c r="P6" t="str">
-        <v>A short suede blouson, clean shoulders and a buttoned tab at the waist.</v>
+        <v>240 gsm cotton, straight cut, a ribbed collar that holds.</v>
       </c>
       <c r="Q6" t="str">
-        <v>Cuir velours de chèvre, doublure coton.</v>
+        <v>100% coton 240 g/m².</v>
       </c>
       <c r="R6" t="str">
-        <v>جلد شامواه ديال المعز، بطانة قطن.</v>
+        <v>100% قطن 240 غ/م².</v>
       </c>
       <c r="S6" t="str">
-        <v>Goat suede, cotton lining.</v>
+        <v>100% cotton, 240 gsm.</v>
       </c>
       <c r="T6" t="str">
-        <v>Nettoyage à sec spécialisé cuir.</v>
+        <v>Lavage à 30°C.</v>
       </c>
       <c r="U6" t="str">
-        <v>التنظيف الجاف المتخصص فالجلد.</v>
+        <v>غسيل على 30°.</v>
       </c>
       <c r="V6" t="str">
-        <v>Specialist leather dry clean only.</v>
+        <v>Wash at 30°C.</v>
       </c>
       <c r="W6" t="str">
-        <v>https://picsum.photos/seed/eh-veste-1/1200/1600;https://picsum.photos/seed/eh-veste-2/1200/1600</v>
+        <v/>
       </c>
       <c r="X6">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="Y6">
-        <v>41</v>
+        <v>152</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>EH-0004</v>
+        <v>EH-JKT-01</v>
       </c>
       <c r="B7" t="str">
         <v>oui</v>
@@ -794,66 +788,66 @@
         <v>nouveautes</v>
       </c>
       <c r="E7" t="str">
-        <v>Pull Rif</v>
+        <v>Bomber léger</v>
       </c>
       <c r="F7" t="str">
-        <v>تريكو الريف</v>
+        <v>بومبر خفيف</v>
       </c>
       <c r="G7" t="str">
-        <v>Rif Knit</v>
+        <v>Lightweight bomber</v>
       </c>
       <c r="H7">
-        <v>780</v>
+        <v>450</v>
       </c>
       <c r="J7" t="str">
-        <v>Essentiel</v>
+        <v>Dernières pièces</v>
       </c>
       <c r="K7" t="str">
-        <v>Écru:#E7E0D2|Anthracite:#33342F|Terracotta:#B4552F</v>
+        <v>Noir:#111111|Kaki:#767676</v>
       </c>
       <c r="L7" t="str">
-        <v>S;M;L;XL;XXL</v>
+        <v>M;L;XL</v>
       </c>
       <c r="N7" t="str">
-        <v>Une maille fine 12 jauge qui se porte seule ou sous une veste sans épaisseur.</v>
+        <v>Bomber léger, col côtelé, doublure filet. Pour l'entre-saison.</v>
       </c>
       <c r="O7" t="str">
-        <v>تريكو رقيق كيتلبس بوحدو ولا تحت جاكيط بلا ما يزيد حجم.</v>
+        <v>بومبر خفيف، ياقة مضلعة، وبطانة شبكية. لبين الفصول.</v>
       </c>
       <c r="P7" t="str">
-        <v>A fine 12-gauge knit that works alone or under a jacket without bulk.</v>
+        <v>Light bomber, ribbed collar, mesh lining. For the in-between months.</v>
       </c>
       <c r="Q7" t="str">
-        <v>100% laine mérinos extra-fine.</v>
+        <v>Nylon, doublure polyester.</v>
       </c>
       <c r="R7" t="str">
-        <v>100% صوف ميرينو رقيق جداً.</v>
+        <v>نايلون، وبطانة بوليستر.</v>
       </c>
       <c r="S7" t="str">
-        <v>100% extra-fine merino wool.</v>
+        <v>Nylon, polyester lining.</v>
       </c>
       <c r="T7" t="str">
-        <v>Lavage à la main à froid, séchage à plat.</v>
+        <v>Lavage à froid.</v>
       </c>
       <c r="U7" t="str">
-        <v>غسيل باليد بالماء البارد، والتنشيف مبسوط.</v>
+        <v>غسيل بالماء البارد.</v>
       </c>
       <c r="V7" t="str">
-        <v>Hand wash cold, dry flat.</v>
+        <v>Cold wash.</v>
       </c>
       <c r="W7" t="str">
-        <v>https://picsum.photos/seed/eh-pull-1/1200/1600;https://picsum.photos/seed/eh-pull-2/1200/1600</v>
+        <v/>
       </c>
       <c r="X7">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="Y7">
-        <v>203</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>EH-0005</v>
+        <v>EH-SWT-01</v>
       </c>
       <c r="B8" t="str">
         <v>oui</v>
@@ -865,527 +859,385 @@
         <v>nouveautes</v>
       </c>
       <c r="E8" t="str">
-        <v>Chemise Oualidia</v>
+        <v>Sweat col rond</v>
       </c>
       <c r="F8" t="str">
-        <v>قميص الوليدية</v>
+        <v>سويت شيرت ياقة دائرية</v>
       </c>
       <c r="G8" t="str">
-        <v>Oualidia Shirt</v>
+        <v>Crewneck sweatshirt</v>
       </c>
       <c r="H8">
-        <v>520</v>
+        <v>260</v>
       </c>
       <c r="K8" t="str">
-        <v>Écru:#E7E0D2|Pierre:#B9B3A6|Indigo:#2E4260</v>
+        <v>Gris:#767676|Noir:#111111</v>
       </c>
       <c r="L8" t="str">
         <v>S;M;L;XL</v>
       </c>
-      <c r="M8" t="str">
-        <v>S</v>
-      </c>
       <c r="N8" t="str">
-        <v>Lin lavé en pièce, col cubain qui reste ouvert, coupe droite et ample.</v>
+        <v>Col rond, coupe droite, bords côtelés.</v>
       </c>
       <c r="O8" t="str">
-        <v>كتان مغسول، ياقة كوبية كتبقى محلولة، وقصة مستقيمة وواسعة.</v>
+        <v>ياقة دائرية، قصة مستقيمة، وأطراف مضلعة.</v>
       </c>
       <c r="P8" t="str">
-        <v>Piece-washed linen, a camp collar that stays open, straight and easy.</v>
+        <v>Crewneck, straight cut, ribbed trims.</v>
       </c>
       <c r="Q8" t="str">
-        <v>100% lin européen lavé.</v>
+        <v>70% coton, 30% polyester.</v>
       </c>
       <c r="R8" t="str">
-        <v>100% كتان أوروبي مغسول.</v>
+        <v>70% قطن، 30% بوليستر.</v>
       </c>
       <c r="S8" t="str">
-        <v>100% washed European linen.</v>
+        <v>70% cotton, 30% polyester.</v>
       </c>
       <c r="T8" t="str">
-        <v>Lavage à 30°C, le froissé fait partie du tissu.</v>
+        <v>Lavage à 30°C.</v>
       </c>
       <c r="U8" t="str">
-        <v>غسيل على 30°، والتجعيد جزء من القماش.</v>
+        <v>غسيل على 30°.</v>
       </c>
       <c r="V8" t="str">
-        <v>Wash at 30°C; the creasing is part of the cloth.</v>
+        <v>Wash at 30°C.</v>
       </c>
       <c r="W8" t="str">
-        <v>https://picsum.photos/seed/eh-lin-1/1200/1600;https://picsum.photos/seed/eh-lin-2/1200/1600</v>
-      </c>
-      <c r="X8">
-        <v>4.5</v>
-      </c>
-      <c r="Y8">
-        <v>64</v>
+        <v/>
+      </c>
+      <c r="X8" t="str">
+        <v/>
+      </c>
+      <c r="Y8" t="str">
+        <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>EH-0006</v>
+        <v>EH-SNK-02</v>
       </c>
       <c r="B9" t="str">
         <v>oui</v>
       </c>
       <c r="C9">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D9" t="str">
-        <v>nouveautes</v>
+        <v>sneakers</v>
       </c>
       <c r="E9" t="str">
-        <v>Écharpe Chefchaouen</v>
+        <v>Sneaker running mesh</v>
       </c>
       <c r="F9" t="str">
-        <v>شال شفشاون</v>
+        <v>سنيكر رانينڭ ميش</v>
       </c>
       <c r="G9" t="str">
-        <v>Chefchaouen Scarf</v>
+        <v>Mesh running sneaker</v>
       </c>
       <c r="H9">
-        <v>450</v>
+        <v>480</v>
+      </c>
+      <c r="J9" t="str">
+        <v>Nouveauté</v>
       </c>
       <c r="K9" t="str">
-        <v>Indigo:#2E4260|Terracotta:#B4552F</v>
+        <v>Blanc:#FFFFFF|Noir:#111111</v>
       </c>
       <c r="L9" t="str">
-        <v>Taille unique</v>
+        <v>40;41;42;43;44;45</v>
       </c>
       <c r="N9" t="str">
-        <v>Tissée sur métier traditionnel, franges nouées main, 200 cm de long.</v>
+        <v>Tige en mesh respirant, semelle amortie. Léger au pied.</v>
       </c>
       <c r="O9" t="str">
-        <v>منسوجة على نول تقليدي، وأطرافها معقودة باليد، طولها 200 سم.</v>
+        <v>ميش كيتنفس، وسمال مريح. خفيف فالرجل.</v>
       </c>
       <c r="P9" t="str">
-        <v>Woven on a traditional loom, hand-knotted fringes, 200 cm long.</v>
+        <v>Breathable mesh upper, cushioned sole. Light on the foot.</v>
       </c>
       <c r="Q9" t="str">
-        <v>100% laine d'agneau.</v>
+        <v>Mesh polyester, semelle EVA.</v>
       </c>
       <c r="R9" t="str">
-        <v>100% صوف الحولي.</v>
+        <v>ميش بوليستر، وسمال EVA.</v>
       </c>
       <c r="S9" t="str">
-        <v>100% lambswool.</v>
+        <v>Polyester mesh, EVA sole.</v>
       </c>
       <c r="T9" t="str">
-        <v>Nettoyage à sec.</v>
+        <v>Nettoyer à la main.</v>
       </c>
       <c r="U9" t="str">
-        <v>التنظيف الجاف.</v>
+        <v>نقيها باليد.</v>
       </c>
       <c r="V9" t="str">
-        <v>Dry clean.</v>
+        <v>Clean by hand.</v>
       </c>
       <c r="W9" t="str">
-        <v>https://picsum.photos/seed/eh-echarpe-1/1200/1600</v>
-      </c>
-      <c r="X9" t="str">
-        <v/>
-      </c>
-      <c r="Y9" t="str">
-        <v/>
+        <v/>
+      </c>
+      <c r="X9">
+        <v>4.3</v>
+      </c>
+      <c r="Y9">
+        <v>41</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>EH-0007</v>
+        <v>EH-SNK-03</v>
       </c>
       <c r="B10" t="str">
         <v>oui</v>
       </c>
       <c r="C10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D10" t="str">
-        <v>tailleur</v>
+        <v>sneakers</v>
       </c>
       <c r="E10" t="str">
-        <v>Costume Casablanca</v>
+        <v>Sneaker cuir blanche</v>
       </c>
       <c r="F10" t="str">
-        <v>بدلة الدار البيضاء</v>
+        <v>سنيكر جلد بيضا</v>
       </c>
       <c r="G10" t="str">
-        <v>Casablanca Suit</v>
+        <v>White leather sneaker</v>
       </c>
       <c r="H10">
-        <v>4900</v>
+        <v>590</v>
+      </c>
+      <c r="I10">
+        <v>690</v>
       </c>
       <c r="J10" t="str">
-        <v>Nouveauté</v>
+        <v>Promo</v>
       </c>
       <c r="K10" t="str">
-        <v>Marine:#252F45|Anthracite:#33342F</v>
+        <v>Blanc:#FFFFFF</v>
       </c>
       <c r="L10" t="str">
-        <v>46;48;50;52;54</v>
+        <v>40;41;42;43;44</v>
       </c>
       <c r="M10" t="str">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="N10" t="str">
-        <v>Deux boutons, revers crantés moyens, épaule napolitaine peu construite.</v>
+        <v>Cuir lisse, forme classique, semelle blanche.</v>
       </c>
       <c r="O10" t="str">
-        <v>زرين، ياقة متوسطة، وكتف نابوليتاني خفيف.</v>
+        <v>جلد أملس، شكل كلاسيكي، وسمال بيض.</v>
       </c>
       <c r="P10" t="str">
-        <v>Two buttons, medium notch lapels, a lightly built Neapolitan shoulder.</v>
+        <v>Smooth leather, classic shape, white sole.</v>
       </c>
       <c r="Q10" t="str">
-        <v>100% laine fresco 260 g/m².</v>
+        <v>Cuir, semelle caoutchouc.</v>
       </c>
       <c r="R10" t="str">
-        <v>100% صوف فريسكو 260 غ/م².</v>
+        <v>جلد، وسمال ديال الكاوتشو.</v>
       </c>
       <c r="S10" t="str">
-        <v>100% fresco wool, 260 gsm.</v>
+        <v>Leather, rubber sole.</v>
       </c>
       <c r="T10" t="str">
-        <v>Nettoyage à sec. Brosser après chaque port.</v>
+        <v>Chiffon humide.</v>
       </c>
       <c r="U10" t="str">
-        <v>التنظيف الجاف. فرشيها من بعد كل لبسة.</v>
+        <v>خرقة مبللة.</v>
       </c>
       <c r="V10" t="str">
-        <v>Dry clean. Brush after each wear.</v>
+        <v>Damp cloth.</v>
       </c>
       <c r="W10" t="str">
-        <v>https://picsum.photos/seed/eh-costume-1/1200/1600;https://picsum.photos/seed/eh-costume-2/1200/1600</v>
+        <v/>
       </c>
       <c r="X10">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Y10">
-        <v>27</v>
+        <v>63</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>EH-0008</v>
+        <v>EH-SNK-04</v>
       </c>
       <c r="B11" t="str">
         <v>oui</v>
       </c>
       <c r="C11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D11" t="str">
-        <v>tailleur</v>
+        <v>sneakers</v>
       </c>
       <c r="E11" t="str">
-        <v>Blazer Rabat</v>
+        <v>Sneaker montante</v>
       </c>
       <c r="F11" t="str">
-        <v>بليزر الرباط</v>
+        <v>سنيكر عالي</v>
       </c>
       <c r="G11" t="str">
-        <v>Rabat Blazer</v>
+        <v>High-top sneaker</v>
       </c>
       <c r="H11">
-        <v>2890</v>
-      </c>
-      <c r="J11" t="str">
-        <v>Essentiel</v>
+        <v>520</v>
       </c>
       <c r="K11" t="str">
-        <v>Olive:#4B5540|Sable:#CDBFA4|Marine:#252F45</v>
+        <v>Noir:#111111|Blanc:#FFFFFF</v>
       </c>
       <c r="L11" t="str">
-        <v>46;48;50;52</v>
+        <v>40;41;42;43;44;45</v>
       </c>
       <c r="N11" t="str">
-        <v>Sans doublure ni entoilage, monté comme une chemise. Il se plie dans un sac et se remet sans marque.</v>
+        <v>Tige montante, maintien à la cheville.</v>
       </c>
       <c r="O11" t="str">
-        <v>بلا بطانة، مركب بحال قميص. كيتطوى فالساك وكيرجع بلا أثر.</v>
+        <v>عالي، وكيشد الكعب مزيان.</v>
       </c>
       <c r="P11" t="str">
-        <v>Unlined and uncanvassed, built like a shirt. It folds into a bag and comes back unmarked.</v>
+        <v>High cut, holds the ankle.</v>
       </c>
       <c r="Q11" t="str">
-        <v>62% laine, 38% lin.</v>
+        <v>Toile et cuir.</v>
       </c>
       <c r="R11" t="str">
-        <v>62% صوف، 38% كتان.</v>
+        <v>توال وجلد.</v>
       </c>
       <c r="S11" t="str">
-        <v>62% wool, 38% linen.</v>
+        <v>Canvas and leather.</v>
       </c>
       <c r="T11" t="str">
-        <v>Nettoyage à sec.</v>
+        <v>Brosse douce.</v>
       </c>
       <c r="U11" t="str">
-        <v>التنظيف الجاف.</v>
+        <v>فرشاة رقيقة.</v>
       </c>
       <c r="V11" t="str">
-        <v>Dry clean.</v>
+        <v>Soft brush.</v>
       </c>
       <c r="W11" t="str">
-        <v>https://picsum.photos/seed/eh-blazer-1/1200/1600;https://picsum.photos/seed/eh-blazer-2/1200/1600</v>
+        <v/>
       </c>
       <c r="X11">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="Y11">
-        <v>52</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>EH-0009</v>
+        <v>EH-CAP-01</v>
       </c>
       <c r="B12" t="str">
         <v>oui</v>
       </c>
-      <c r="C12">
-        <v>3</v>
+      <c r="C12" t="str">
+        <v/>
       </c>
       <c r="D12" t="str">
-        <v>tailleur</v>
+        <v>casquettes</v>
       </c>
       <c r="E12" t="str">
-        <v>Pantalon Fès</v>
+        <v>Casquette snapback</v>
       </c>
       <c r="F12" t="str">
-        <v>سروال فاس</v>
+        <v>كاسكيطة سناباك</v>
       </c>
       <c r="G12" t="str">
-        <v>Fes Trousers</v>
+        <v>Snapback cap</v>
       </c>
       <c r="H12">
-        <v>890</v>
+        <v>90</v>
       </c>
       <c r="K12" t="str">
-        <v>Anthracite:#33342F|Marine:#252F45</v>
+        <v>Noir:#111111|Blanc:#FFFFFF</v>
       </c>
       <c r="L12" t="str">
-        <v>46;48;50;52;54</v>
-      </c>
-      <c r="M12" t="str">
-        <v>54</v>
+        <v>Taille unique</v>
       </c>
       <c r="N12" t="str">
-        <v>Taille haute tenue par des pattes de serrage latérales, une pince simple, jambe légèrement fuselée.</v>
+        <v>Visière plate, réglage snapback.</v>
       </c>
       <c r="O12" t="str">
-        <v>وسط عالي مشدود بشرائط جانبية، طية وحدة، وساق ضيقة شوية.</v>
+        <v>فيزيير مسطح، وريڭلاج سناباك.</v>
       </c>
       <c r="P12" t="str">
-        <v>A high waist held by side adjusters, a single pleat, a lightly tapered leg.</v>
+        <v>Flat brim, snapback closure.</v>
       </c>
       <c r="Q12" t="str">
-        <v>100% laine vierge.</v>
+        <v>Coton.</v>
       </c>
       <c r="R12" t="str">
-        <v>100% صوف بكر.</v>
+        <v>قطن.</v>
       </c>
       <c r="S12" t="str">
-        <v>100% virgin wool.</v>
+        <v>Cotton.</v>
       </c>
       <c r="T12" t="str">
-        <v>Nettoyage à sec.</v>
+        <v>Lavage à la main.</v>
       </c>
       <c r="U12" t="str">
-        <v>التنظيف الجاف.</v>
+        <v>غسيل باليد.</v>
       </c>
       <c r="V12" t="str">
-        <v>Dry clean.</v>
+        <v>Hand wash.</v>
       </c>
       <c r="W12" t="str">
-        <v>https://picsum.photos/seed/eh-pantalon-1/1200/1600;https://picsum.photos/seed/eh-pantalon-2/1200/1600</v>
-      </c>
-      <c r="X12">
-        <v>4.5</v>
-      </c>
-      <c r="Y12">
-        <v>73</v>
+        <v/>
+      </c>
+      <c r="X12" t="str">
+        <v/>
+      </c>
+      <c r="Y12" t="str">
+        <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>EH-0010</v>
+        <v>EH-OLD-99</v>
       </c>
       <c r="B13" t="str">
-        <v>oui</v>
+        <v>non</v>
       </c>
       <c r="C13">
-        <v>4</v>
+        <v>99</v>
       </c>
       <c r="D13" t="str">
-        <v>tailleur</v>
+        <v>promos</v>
       </c>
       <c r="E13" t="str">
-        <v>Gilet Meknès</v>
-      </c>
-      <c r="F13" t="str">
-        <v>صدرية مكناس</v>
-      </c>
-      <c r="G13" t="str">
-        <v>Meknes Waistcoat</v>
+        <v>Retiré</v>
       </c>
       <c r="H13">
-        <v>990</v>
-      </c>
-      <c r="J13" t="str">
-        <v>Dernières pièces</v>
+        <v>100</v>
       </c>
       <c r="K13" t="str">
-        <v>Anthracite:#33342F|Havane:#6B4A32</v>
+        <v>Noir:#111111</v>
       </c>
       <c r="L13" t="str">
-        <v>46;48;50</v>
+        <v>M</v>
       </c>
       <c r="N13" t="str">
-        <v>Cinq boutons, dos en cupro ajusté par une martingale.</v>
-      </c>
-      <c r="O13" t="str">
-        <v>خمسة زرار، والظهر ديال الكوبرو مشدود بحزام.</v>
-      </c>
-      <c r="P13" t="str">
-        <v>Five buttons, a cupro back adjusted by a strap.</v>
+        <v>—</v>
       </c>
       <c r="Q13" t="str">
-        <v>100% laine grattée, dos cupro.</v>
-      </c>
-      <c r="R13" t="str">
-        <v>100% صوف ممشط، ظهر كوبرو.</v>
-      </c>
-      <c r="S13" t="str">
-        <v>100% brushed wool, cupro back.</v>
+        <v>—</v>
       </c>
       <c r="T13" t="str">
-        <v>Nettoyage à sec.</v>
-      </c>
-      <c r="U13" t="str">
-        <v>التنظيف الجاف.</v>
-      </c>
-      <c r="V13" t="str">
-        <v>Dry clean.</v>
+        <v>—</v>
       </c>
       <c r="W13" t="str">
-        <v>https://picsum.photos/seed/eh-gilet-1/1200/1600;https://picsum.photos/seed/eh-gilet-2/1200/1600</v>
-      </c>
-      <c r="X13">
-        <v>4.6</v>
-      </c>
-      <c r="Y13">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>EH-0099</v>
-      </c>
-      <c r="B14" t="str">
-        <v>non</v>
-      </c>
-      <c r="C14">
-        <v>99</v>
-      </c>
-      <c r="D14" t="str">
-        <v>nouveautes</v>
-      </c>
-      <c r="E14" t="str">
-        <v>Pièce retirée</v>
-      </c>
-      <c r="H14">
-        <v>100</v>
-      </c>
-      <c r="K14" t="str">
-        <v>Noir:#000000</v>
-      </c>
-      <c r="L14" t="str">
-        <v>M</v>
-      </c>
-      <c r="N14" t="str">
-        <v>—</v>
-      </c>
-      <c r="Q14" t="str">
-        <v>—</v>
-      </c>
-      <c r="T14" t="str">
-        <v>—</v>
-      </c>
-      <c r="W14" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>EH-0011</v>
-      </c>
-      <c r="B15" t="str">
-        <v>oui</v>
-      </c>
-      <c r="C15" t="str">
-        <v/>
-      </c>
-      <c r="D15" t="str">
-        <v>nouveautes</v>
-      </c>
-      <c r="E15" t="str">
-        <v>Ceinture Fès</v>
-      </c>
-      <c r="F15" t="str">
-        <v>حزام فاس</v>
-      </c>
-      <c r="G15" t="str">
-        <v>Fes Belt</v>
-      </c>
-      <c r="H15">
-        <v>390</v>
-      </c>
-      <c r="K15" t="str">
-        <v>Havane:#6B4A32|Noir:#16160F</v>
-      </c>
-      <c r="L15" t="str">
-        <v>85;90;95;100</v>
-      </c>
-      <c r="N15" t="str">
-        <v>Une seule épaisseur de cuir tanné végétal de 3,5 mm, boucle laiton massif.</v>
-      </c>
-      <c r="O15" t="str">
-        <v>طبقة وحدة ديال الجلد المدبوغ نباتياً 3,5 مم، وبوكل نحاس صافي.</v>
-      </c>
-      <c r="P15" t="str">
-        <v>A single thickness of 3.5 mm vegetable-tanned leather, solid brass buckle.</v>
-      </c>
-      <c r="Q15" t="str">
-        <v>Cuir tanné végétal, boucle laiton.</v>
-      </c>
-      <c r="R15" t="str">
-        <v>جلد مدبوغ نباتياً، بوكل نحاس.</v>
-      </c>
-      <c r="S15" t="str">
-        <v>Vegetable-tanned leather, brass buckle.</v>
-      </c>
-      <c r="T15" t="str">
-        <v>Nourrir au baume incolore.</v>
-      </c>
-      <c r="U15" t="str">
-        <v>دهنها ببلسم بلا لون.</v>
-      </c>
-      <c r="V15" t="str">
-        <v>Feed with a colourless balm.</v>
-      </c>
-      <c r="W15" t="str">
-        <v>https://picsum.photos/seed/eh-ceinture-1/1200/1600;https://picsum.photos/seed/eh-ceinture-2/1200/1600</v>
-      </c>
-      <c r="X15">
-        <v>4.6</v>
-      </c>
-      <c r="Y15">
-        <v>112</v>
+        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Y15"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Y13"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/catalogue-sample.xlsx
+++ b/data/catalogue-sample.xlsx
@@ -619,11 +619,11 @@
       <c r="W4" t="str">
         <v/>
       </c>
-      <c r="X4">
-        <v>4.5</v>
-      </c>
-      <c r="Y4">
-        <v>34</v>
+      <c r="X4" t="str">
+        <v/>
+      </c>
+      <c r="Y4" t="str">
+        <v/>
       </c>
     </row>
     <row r="5">
@@ -696,11 +696,11 @@
       <c r="W5" t="str">
         <v/>
       </c>
-      <c r="X5">
-        <v>4.7</v>
-      </c>
-      <c r="Y5">
-        <v>88</v>
+      <c r="X5" t="str">
+        <v/>
+      </c>
+      <c r="Y5" t="str">
+        <v/>
       </c>
     </row>
     <row r="6">
@@ -767,11 +767,11 @@
       <c r="W6" t="str">
         <v/>
       </c>
-      <c r="X6">
-        <v>4.6</v>
-      </c>
-      <c r="Y6">
-        <v>152</v>
+      <c r="X6" t="str">
+        <v/>
+      </c>
+      <c r="Y6" t="str">
+        <v/>
       </c>
     </row>
     <row r="7">
@@ -838,11 +838,11 @@
       <c r="W7" t="str">
         <v/>
       </c>
-      <c r="X7">
-        <v>4.4</v>
-      </c>
-      <c r="Y7">
-        <v>27</v>
+      <c r="X7" t="str">
+        <v/>
+      </c>
+      <c r="Y7" t="str">
+        <v/>
       </c>
     </row>
     <row r="8">
@@ -977,11 +977,11 @@
       <c r="W9" t="str">
         <v/>
       </c>
-      <c r="X9">
-        <v>4.3</v>
-      </c>
-      <c r="Y9">
-        <v>41</v>
+      <c r="X9" t="str">
+        <v/>
+      </c>
+      <c r="Y9" t="str">
+        <v/>
       </c>
     </row>
     <row r="10">
@@ -1054,11 +1054,11 @@
       <c r="W10" t="str">
         <v/>
       </c>
-      <c r="X10">
-        <v>4.8</v>
-      </c>
-      <c r="Y10">
-        <v>63</v>
+      <c r="X10" t="str">
+        <v/>
+      </c>
+      <c r="Y10" t="str">
+        <v/>
       </c>
     </row>
     <row r="11">
@@ -1122,11 +1122,11 @@
       <c r="W11" t="str">
         <v/>
       </c>
-      <c r="X11">
-        <v>4.2</v>
-      </c>
-      <c r="Y11">
-        <v>19</v>
+      <c r="X11" t="str">
+        <v/>
+      </c>
+      <c r="Y11" t="str">
+        <v/>
       </c>
     </row>
     <row r="12">
